--- a/consulting_forms/020_massage_consultation_form--consulting_forms.xlsx
+++ b/consulting_forms/020_massage_consultation_form--consulting_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Patient Name</t>
+          <t>1. Patient Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Contact Number</t>
+          <t>2. Contact Number</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Email Address</t>
+          <t>3. Email Address</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,59 +594,59 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Consultation Date</t>
+          <t>4. Consultation Date</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>consultation_time</t>
+          <t>massage_services</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Consultation Time</t>
+          <t>5. Massage Services</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>massage_services</t>
+          <t>benefits_of_massage</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Massage Services</t>
+          <t>6. Benefits of Massage</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>benefits_of_massage</t>
+          <t>medical_history</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Benefits of Massage</t>
+          <t>7. Medical History</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,25 +681,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>medical_history</t>
+          <t>massage_therapist</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>8. Massage Therapist</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,13 +709,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Massage Frequency</t>
+          <t>9. Massage Frequency</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>pain_level</t>
+          <t>massage_therapist_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pain Level</t>
+          <t>10. Massage Therapist</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pain_type</t>
+          <t>pain_level</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pain Type</t>
+          <t>11. Pain Level</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,315 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>massage_therapist</t>
+          <t>pain_type</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Massage Therapist</t>
+          <t>12. Pain Type</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>massage_duration</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Massage Duration</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>massage_frequency_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Massage Frequency</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>massage_frequency_3</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>How often do you plan on getting massage</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>massage_frequency_4</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Massage Frequency</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>massage_frequency_5</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Massage Frequency</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>massage_frequency_6</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Massage Frequency</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>massage_frequency_7</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Massage Frequency</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>massage_frequency_8</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Massage Frequency</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>massage_frequency_9</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Massage Frequency</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>massage_frequency_10</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Massage Frequency</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>massage_frequency_11</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Massage Frequency</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>massage_frequency_12</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Massage Frequency</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>massage_frequency_13</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Massage Frequency</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1194,136 +895,85 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>massage_services_choices</t>
+          <t>massage_frequency_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>1_time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>1 time</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>massage_services_choices</t>
+          <t>massage_frequency_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hot_stone</t>
+          <t>2_times_a_week</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hot Stone</t>
+          <t>2 times a week</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>massage_services_choices</t>
+          <t>massage_frequency_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>trigger_point</t>
+          <t>3_times_a_week</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Trigger Point</t>
+          <t>3 times a week</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>massage_services_choices</t>
+          <t>massage_frequency_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>craniosacral</t>
+          <t>4_times_a_week</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Craniosacral</t>
+          <t>4 times a week</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>massage_services_choices</t>
+          <t>massage_frequency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>cupping</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cupping</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>massage_services_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>myofascial</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Myofascial</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>massage_services_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ortho</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ortho</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>massage_services_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>polarity</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Polarity</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
